--- a/MAJEntreesCDA/ig/StructureDefinition-fr-cda-instructions-au-dispensateur.xlsx
+++ b/MAJEntreesCDA/ig/StructureDefinition-fr-cda-instructions-au-dispensateur.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$72</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1942" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2291" uniqueCount="264">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T09:38:07+00:00</t>
+    <t>2026-04-20T13:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -549,126 +549,114 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ActCode</t>
   </si>
   <si>
-    <t>Act.text</t>
+    <t>Act.code.nullFlavor</t>
+  </si>
+  <si>
+    <t>Act.code.code</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>FINSTRUCT</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>Act.code.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>1.3.6.1.4.1.19376.1.5.3.2</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>Act.code.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>IHEActCode</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>Act.code.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Act.code.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>Act.code.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>Act.code.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Act.code.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
 </t>
   </si>
   <si>
-    <t>Instructions au dispensateur sous forme textuelle.</t>
-  </si>
-  <si>
-    <t>Act.statusCode</t>
-  </si>
-  <si>
-    <t>Statut de l’entrée. Fixé à la valeur 'completed'</t>
-  </si>
-  <si>
-    <t>Statut de l’entrée</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActStatus</t>
-  </si>
-  <si>
-    <t>Act.statusCode.nullFlavor</t>
-  </si>
-  <si>
-    <t>Act.statusCode.code</t>
-  </si>
-  <si>
-    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
-  </si>
-  <si>
-    <t>completed</t>
-  </si>
-  <si>
-    <t>CD.code</t>
-  </si>
-  <si>
-    <t>Act.statusCode.codeSystem</t>
-  </si>
-  <si>
-    <t>Code System</t>
-  </si>
-  <si>
-    <t>Specifies the code system that defines the code.</t>
-  </si>
-  <si>
-    <t>CD.codeSystem</t>
-  </si>
-  <si>
-    <t>Act.statusCode.codeSystemName</t>
-  </si>
-  <si>
-    <t>Code System Name</t>
-  </si>
-  <si>
-    <t>The common name of the coding system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemName</t>
-  </si>
-  <si>
-    <t>Act.statusCode.codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Code System Version</t>
-  </si>
-  <si>
-    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Act.statusCode.displayName</t>
-  </si>
-  <si>
-    <t>Display Name</t>
-  </si>
-  <si>
-    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
-  </si>
-  <si>
-    <t>CD.displayName</t>
-  </si>
-  <si>
-    <t>Act.statusCode.sdtcValueSet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
-</t>
-  </si>
-  <si>
-    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.valueSet</t>
-  </si>
-  <si>
-    <t>Act.statusCode.sdtcValueSetVersion</t>
-  </si>
-  <si>
-    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.sdtcValueSetVersion</t>
-  </si>
-  <si>
-    <t>Act.statusCode.originalText</t>
-  </si>
-  <si>
-    <t>Original Text</t>
-  </si>
-  <si>
     <t>The text or phrase used as the basis for the coding.</t>
   </si>
   <si>
     <t>CD.originalText</t>
   </si>
   <si>
-    <t>Act.statusCode.qualifier</t>
+    <t>Act.code.qualifier</t>
   </si>
   <si>
     <t>Qualifier</t>
@@ -684,16 +672,70 @@
     <t>CD.qualifier</t>
   </si>
   <si>
+    <t>Act.code.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
+  </si>
+  <si>
+    <t>Act.text</t>
+  </si>
+  <si>
+    <t>Instructions au dispensateur sous forme textuelle.</t>
+  </si>
+  <si>
+    <t>Act.statusCode</t>
+  </si>
+  <si>
+    <t>Statut de l’entrée. Fixé à la valeur 'completed'</t>
+  </si>
+  <si>
+    <t>Statut de l’entrée</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActStatus</t>
+  </si>
+  <si>
+    <t>Act.statusCode.nullFlavor</t>
+  </si>
+  <si>
+    <t>Act.statusCode.code</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>Act.statusCode.codeSystem</t>
+  </si>
+  <si>
+    <t>Act.statusCode.codeSystemName</t>
+  </si>
+  <si>
+    <t>Act.statusCode.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Act.statusCode.displayName</t>
+  </si>
+  <si>
+    <t>Act.statusCode.sdtcValueSet</t>
+  </si>
+  <si>
+    <t>Act.statusCode.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Act.statusCode.originalText</t>
+  </si>
+  <si>
+    <t>Act.statusCode.qualifier</t>
+  </si>
+  <si>
     <t>Act.statusCode.translation</t>
-  </si>
-  <si>
-    <t>Translation</t>
-  </si>
-  <si>
-    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
-  </si>
-  <si>
-    <t>CD.translation</t>
   </si>
   <si>
     <t>Act.effectiveTime</t>
@@ -1110,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK61"/>
+  <dimension ref="A1:AK72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.84765625" customWidth="true" bestFit="true"/>
@@ -4629,7 +4671,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>173</v>
       </c>
@@ -4640,15 +4682,17 @@
       <c r="D35" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E35" s="2"/>
+      <c r="E35" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F35" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>74</v>
@@ -4657,12 +4701,12 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="M35" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="L35" s="2"/>
+      <c r="M35" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -4688,13 +4732,11 @@
         <v>74</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>74</v>
@@ -4712,7 +4754,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>173</v>
+        <v>89</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4732,16 +4774,18 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E36" s="2"/>
+      <c r="E36" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F36" t="s" s="2">
         <v>75</v>
       </c>
@@ -4758,13 +4802,11 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4776,7 +4818,7 @@
         <v>74</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>74</v>
+        <v>176</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>74</v>
@@ -4791,11 +4833,13 @@
         <v>74</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y36" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z36" t="s" s="2">
-        <v>179</v>
+        <v>74</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>74</v>
@@ -4813,7 +4857,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4831,28 +4875,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -4861,11 +4905,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>86</v>
+        <v>180</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4877,7 +4921,7 @@
         <v>74</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>74</v>
+        <v>181</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>74</v>
@@ -4892,11 +4936,13 @@
         <v>74</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y37" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z37" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>74</v>
@@ -4914,7 +4960,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>89</v>
+        <v>182</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -4934,17 +4980,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>62</v>
+        <v>184</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -4962,11 +5008,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4978,7 +5024,7 @@
         <v>74</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>74</v>
@@ -5017,7 +5063,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5037,23 +5083,23 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>74</v>
@@ -5065,11 +5111,11 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5120,7 +5166,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5140,23 +5186,23 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>74</v>
@@ -5172,7 +5218,7 @@
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5223,7 +5269,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5243,23 +5289,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E41" t="s" s="2">
-        <v>194</v>
-      </c>
+      <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>74</v>
@@ -5271,11 +5315,11 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>102</v>
+        <v>197</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5326,7 +5370,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5346,23 +5390,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E42" t="s" s="2">
-        <v>198</v>
-      </c>
+      <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>74</v>
@@ -5378,7 +5420,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5429,7 +5471,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5449,16 +5491,18 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E43" s="2"/>
+      <c r="E43" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
@@ -5475,11 +5519,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5530,7 +5574,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5550,21 +5594,23 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E44" s="2"/>
+      <c r="E44" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>74</v>
@@ -5576,11 +5622,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>102</v>
+        <v>210</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5631,13 +5677,13 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>74</v>
@@ -5651,23 +5697,23 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>74</v>
@@ -5679,11 +5725,11 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5734,13 +5780,13 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>74</v>
@@ -5752,28 +5798,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E46" t="s" s="2">
-        <v>213</v>
-      </c>
+      <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>74</v>
@@ -5782,12 +5826,12 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="L46" s="2"/>
-      <c r="M46" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M46" s="2"/>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -5837,13 +5881,13 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>74</v>
@@ -5855,28 +5899,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E47" t="s" s="2">
-        <v>218</v>
-      </c>
+      <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -5885,11 +5927,13 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="L47" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="M47" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -5916,13 +5960,11 @@
         <v>74</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>74</v>
+        <v>222</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>74</v>
@@ -5940,13 +5982,13 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>74</v>
@@ -5960,16 +6002,18 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E48" s="2"/>
+      <c r="E48" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
@@ -5986,10 +6030,12 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>222</v>
+        <v>85</v>
       </c>
       <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
+      <c r="M48" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6015,13 +6061,11 @@
         <v>74</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>74</v>
@@ -6039,7 +6083,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>221</v>
+        <v>89</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6059,16 +6103,18 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E49" s="2"/>
+      <c r="E49" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
@@ -6085,10 +6131,12 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>224</v>
+        <v>85</v>
       </c>
       <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
+      <c r="M49" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6099,7 +6147,7 @@
         <v>74</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>74</v>
+        <v>225</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>74</v>
@@ -6114,11 +6162,13 @@
         <v>74</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="Y49" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z49" t="s" s="2">
-        <v>225</v>
+        <v>74</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>74</v>
@@ -6136,7 +6186,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>223</v>
+        <v>177</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6165,12 +6215,14 @@
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E50" s="2"/>
+      <c r="E50" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>74</v>
@@ -6182,10 +6234,12 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
+      <c r="M50" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -6211,11 +6265,13 @@
         <v>74</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>227</v>
+        <v>74</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>74</v>
@@ -6233,7 +6289,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>226</v>
+        <v>182</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6253,21 +6309,23 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E51" s="2"/>
+      <c r="E51" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>74</v>
@@ -6279,10 +6337,12 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>229</v>
+        <v>102</v>
       </c>
       <c r="L51" s="2"/>
-      <c r="M51" s="2"/>
+      <c r="M51" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -6332,7 +6392,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>228</v>
+        <v>187</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6352,21 +6412,23 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E52" s="2"/>
+      <c r="E52" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>74</v>
@@ -6378,10 +6440,12 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>231</v>
+        <v>102</v>
       </c>
       <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
+      <c r="M52" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -6431,13 +6495,13 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>230</v>
+        <v>191</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>74</v>
@@ -6451,21 +6515,23 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E53" s="2"/>
+      <c r="E53" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>74</v>
@@ -6477,10 +6543,12 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>233</v>
+        <v>102</v>
       </c>
       <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
+      <c r="M53" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -6530,13 +6598,13 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>232</v>
+        <v>195</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>74</v>
@@ -6550,10 +6618,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6564,7 +6632,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>74</v>
@@ -6576,10 +6644,12 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>235</v>
+        <v>197</v>
       </c>
       <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
+      <c r="M54" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -6629,13 +6699,13 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>74</v>
@@ -6649,10 +6719,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6663,7 +6733,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>74</v>
@@ -6675,10 +6745,12 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>237</v>
+        <v>102</v>
       </c>
       <c r="L55" s="2"/>
-      <c r="M55" s="2"/>
+      <c r="M55" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -6728,13 +6800,13 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>74</v>
@@ -6748,21 +6820,23 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E56" s="2"/>
+      <c r="E56" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>74</v>
@@ -6774,10 +6848,12 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>239</v>
+        <v>205</v>
       </c>
       <c r="L56" s="2"/>
-      <c r="M56" s="2"/>
+      <c r="M56" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -6827,13 +6903,13 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>74</v>
@@ -6847,21 +6923,23 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E57" s="2"/>
+      <c r="E57" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>74</v>
@@ -6873,10 +6951,12 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="L57" s="2"/>
-      <c r="M57" s="2"/>
+      <c r="M57" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -6926,7 +7006,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -6946,21 +7026,23 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E58" s="2"/>
+      <c r="E58" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>74</v>
@@ -6972,10 +7054,12 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>243</v>
+        <v>169</v>
       </c>
       <c r="L58" s="2"/>
-      <c r="M58" s="2"/>
+      <c r="M58" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7025,7 +7109,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7045,10 +7129,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7059,7 +7143,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>74</v>
@@ -7071,7 +7155,7 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -7124,13 +7208,13 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>74</v>
@@ -7144,10 +7228,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7158,7 +7242,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>74</v>
@@ -7170,7 +7254,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7199,13 +7283,11 @@
         <v>74</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>74</v>
+        <v>239</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>74</v>
@@ -7223,13 +7305,13 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>74</v>
@@ -7243,10 +7325,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7257,7 +7339,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>74</v>
@@ -7269,7 +7351,7 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>249</v>
+        <v>91</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -7298,13 +7380,11 @@
         <v>74</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>74</v>
+        <v>241</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>74</v>
@@ -7322,26 +7402,1115 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L64" s="2"/>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AG61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH61" t="s" s="2">
+      <c r="B65" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK61" t="s" s="2">
+      <c r="H65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L66" s="2"/>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L67" s="2"/>
+      <c r="M67" s="2"/>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2"/>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L70" s="2"/>
+      <c r="M70" s="2"/>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L71" s="2"/>
+      <c r="M71" s="2"/>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L72" s="2"/>
+      <c r="M72" s="2"/>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK72" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK61">
+  <autoFilter ref="A1:AK72">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7351,7 +8520,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI60">
+  <conditionalFormatting sqref="A2:AI71">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
